--- a/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-1 位置與位移　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上1-1 位置與位移　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>描述運動要先選定？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>參考點</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>可以</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>基準</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>實際走過的總長度是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>路徑長</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>參考點</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>可以</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>純量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>起點到終點的直線有向距離是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>位移</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>參考點</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>相對</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>路徑長是純量還向量？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>純量</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>只有大小</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>位移是純量還向量？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>有方向</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>繞操場一圈回原點位移是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>5m向東</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>10m向北</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>回原點</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>路徑長恆為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>正</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>非負</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>運動是相對還絕對？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>相對</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>需參考</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>位移與路徑長何者有方向？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>相對</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>位移</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>描述位置的基準點稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>參考點</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-1 位置與位移　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上1-1 位置與位移　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>向東走3m再向東2m,位移？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>10m向北</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>5m向東</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>同向</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>向東走3m再向西3m,位移？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>5m向東</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>抵消</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>向東3m再西3m,路徑長？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>6m</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>總長</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>跑400m操場一圈,路徑長？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>400m</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>實走</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>跑400m操場一圈,位移？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>回原點</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>位移可以為負嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>路徑長</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>可以</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>向量</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>有方向</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>直線同向前進位移與路徑長？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>參考點</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>位移大小一定小於等於路徑長嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>正</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>直線最短</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>向北5m再向北5m位移？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>5m向東</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>10m向北</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>同向</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>繞圓一圈回起點路徑長為零嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>純量</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>可以</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>實走</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上1-1 位置與位移　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上1-1 位置與位移　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>往東走4m再往北走3m,位移大小？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>5m</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>畢氏3-4-5</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何來回運動路徑長大於位移？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>位移只算起終點直線</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>相同(同起終點)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>否,路徑長可不為零</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>路徑40m,位移0</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>定義</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>繞正方形邊長10m一圈,路徑長與位移？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>位移4m北,路徑8m</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>路徑40m,位移0</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>否,路徑長可不為零</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>位移含方向,路徑長只有大小</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>封閉</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>位移為零是否代表沒移動過？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>否,路徑長可不為零</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>位移=直徑,路徑=半周長</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>位移含方向,路徑長只有大小</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>位移只算起終點直線</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>從家到學校抄近路與繞路位移相同嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>位移4m北,路徑8m</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>位移含方向,路徑長只有大小</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>路徑40m,位移0</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>相同(同起終點)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>向北6m向南2m,位移與路徑長？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>路徑40m,位移0</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>位移4m北,路徑8m</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>位移含方向,路徑長只有大小</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>相同(同起終點)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何位移是向量而路徑長是純量？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>位移=直徑,路徑=半周長</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>相同(同起終點)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>路徑40m,位移0</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>位移含方向,路徑長只有大小</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>操場跑半圈(直徑兩端)位移與路徑關係？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>路徑40m,位移0</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>位移=直徑,路徑=半周長</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>相同(同起終點)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>位移4m北,路徑8m</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>幾何</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>向東6m再向北8m位移大小？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>10m</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>6-8-10</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>操場跑兩圈位移是多少？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>5m向東</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>400m</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>回原點</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>基準</t>
+          <t>基準：要說物體動了沒有,一定要先選一個不動的點當比較基準</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>純量</t>
+          <t>純量：路徑長是走過路線的總長度,只算數字大小,不管方向</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：位移是從出發點直直連到終點的距離,還要標出方向</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>只有大小</t>
+          <t>只有大小：路徑長只有長度數字,沒有方向,所以是純量</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>有方向</t>
+          <t>有方向：位移除了距離大小,還一定要說出是往哪個方向</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>回原點</t>
+          <t>回原點：起點和終點是同一個點,直線距離是0,所以位移為零</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>非負</t>
+          <t>非負：只要有移動,走過的路線長度一定是正數或零,不會是負的</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>需參考</t>
+          <t>需參考：物體有沒有在動,要看你選哪個點當參考,答案會不同</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：位移是從起點指向終點的直線距離,有方向性,是向量;路徑長只是走過的總長度,沒有方向</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>基準</t>
+          <t>基準：要描述一個物體的位置,必須先選定一個不動的參考點當作比較的基準</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>同向：兩段路都往東走,方向相同,直接把距離3m加2m等於5m</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>抵消</t>
+          <t>抵消：往東3m又往西3m,兩個方向相反的距離互相抵消,回到原點</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>總長</t>
+          <t>總長：不管方向,只把走過的距離加起來,3m加3m等於6m</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>實走</t>
+          <t>實走：整整繞操場跑了一圈,腳實際踩過的距離就是400公尺</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>回原點</t>
+          <t>回原點：繞一圈後又回到出發的地方,起點終點相同所以位移是零</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>有方向</t>
+          <t>有方向：如果訂向東為正,那麼往西移動的位移數值就會是負的</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>一致：一直往同一個方向走直線,沒有繞路,兩者數字會一樣大</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>直線最短</t>
+          <t>直線最短：兩點之間直線距離最短,繞路走的路徑長只會更長或相等</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>同向：兩次位移方向相同都是向北,可以直接相加,5+5=10公尺向北</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>實走</t>
+          <t>實走：路徑長是實際走過的距離,繞一圈確實走了一段路,只是位移(起點到終點的距離)才是零</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>畢氏3-4-5</t>
+          <t>畢氏3-4-5：東4m和北3m互相垂直,用畢氏定理算出直線距離是5m</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>定義</t>
+          <t>定義：位移只看出發點到終點的直線距離,來回走的路程都白算了</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>封閉</t>
+          <t>封閉：四邊各10m合計走了40m,但又回到起點所以位移為零</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：位移為零只代表回到原地,過程中還是可能走了很長的路</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：只要出發點和終點一樣,不管中間怎麼走,位移都相同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>計算：北6m減去反方向的南2m剩4m北,路徑長則是6m加2m等於8m</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：位移要標出方向才有意義,路徑長只需知道走了多長就好</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>幾何</t>
+          <t>幾何：從一端跑到另一端,直線距離是直徑,實際走的弧線是半圓周長</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>6-8-10</t>
+          <t>6-8-10：東6公尺與北8公尺互相垂直,用畢氏定理6²+8²=100,開根號等於10公尺,這是常見的3-4-5倍數關係</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>回原點</t>
+          <t>回原點：不論跑幾圈,只要最後回到出發點,起點到終點的距離就是0,位移就是0</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上1-1_三種難度測驗卷.xlsx
@@ -763,14 +763,14 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>5m向東</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>6m</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>5m向東</t>
-        </is>
-      </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>0</t>
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>10m向北</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>400m</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>10m向北</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>6m</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>5m向東</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>5m向東</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>5m向東</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>5m向東</t>
+          <t>400m</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>5m向東</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>400m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
